--- a/data/trans_orig/IP16A10-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6944</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22989</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27985</t>
+          <t>27990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>26171</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51746</t>
+          <t>51772</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57440</t>
+          <t>57338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37110</t>
+          <t>37423</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42209</t>
+          <t>42104</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47303</t>
+          <t>47239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86916</t>
+          <t>86715</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92857</t>
+          <t>92949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42347</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4465</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66039</t>
+          <t>65942</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3573</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11637</t>
+          <t>11072</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5721</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113668</t>
+          <t>114233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121846</t>
+          <t>121732</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>137761</t>
+          <t>137003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143250</t>
+          <t>143236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254531</t>
+          <t>254318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263754</t>
+          <t>263503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>5261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44090</t>
+          <t>44177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48362</t>
+          <t>48350</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46744</t>
+          <t>45860</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93353</t>
+          <t>93231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99105</t>
+          <t>99336</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59979</t>
+          <t>60043</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70895</t>
+          <t>71365</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133626</t>
+          <t>134015</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>139275</t>
+          <t>139278</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>3295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29742</t>
+          <t>29199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66537</t>
+          <t>66569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>601</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5182</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27944</t>
+          <t>28019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31973</t>
+          <t>31962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62542</t>
+          <t>62061</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67114</t>
+          <t>67123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1875</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3667</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179467</t>
+          <t>179747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>185869</t>
+          <t>185799</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182150</t>
+          <t>182793</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>188975</t>
+          <t>189536</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364588</t>
+          <t>364838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374175</t>
+          <t>374039</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59105</t>
+          <t>58698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5024,7 +5024,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47620</t>
+          <t>47487</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>44021</t>
+          <t>44009</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93040</t>
+          <t>93254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97903</t>
+          <t>97911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4263</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>37323</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81989</t>
+          <t>81947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>557</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5451</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157880</t>
+          <t>157742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161978</t>
+          <t>161979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142674</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147466</t>
+          <t>147469</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302708</t>
+          <t>302815</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309312</t>
+          <t>309268</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A10-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A10-Edad-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3421</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2770</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5721</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5880</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,54%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3484</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28970</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26234</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26265</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23314</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27990</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23155</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>28025</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,46%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>80,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28970</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>26171</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>51787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57338</t>
+          <t>57388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3592</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2846</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5798</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,59%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>725</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7466</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,28%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50235</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47368</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40375</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37423</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42104</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>36717</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42187</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,41%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>50235</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47239</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>86715</t>
+          <t>86386</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>92949</t>
+          <t>92851</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1181</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4089</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3869</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,25%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,17%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3926</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1180</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4296</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21326</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>18418</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18638</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,75%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>81,83%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,81%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>67</t>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4027</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1309</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4465</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4039</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,87%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38129</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35411</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,79%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38129</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34973</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,68%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>88,68%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>102</t>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>65942</t>
+          <t>65969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2719</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6504</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>6797</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3573</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11072</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3809</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11888</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2719</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6916</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14906</t>
+          <t>15037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>141200</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>137415</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143250</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>118508</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>114233</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>121732</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>113417</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121496</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,58%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,15%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>141200</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>137003</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143236</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>254318</t>
+          <t>254187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263503</t>
+          <t>263501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4369</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1708</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4679</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>493</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4255</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6746</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50234</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46752</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51121</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>47148</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44177</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>48350</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>44601</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48363</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,5%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>50234</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45860</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>51121</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>93231</t>
+          <t>93885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>99336</t>
+          <t>99360</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -2900,52 +2900,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>51121</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51121</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51121</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>48856</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>48856</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>48856</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51121</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51121</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51121</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1589</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5204</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5100</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,44%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5903</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3125,74 +3125,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>74019</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71080</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,13%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>63658</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>60043</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>60147</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,56%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,18%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>74019</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>71365</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,13%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>194</t>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134015</t>
+          <t>133521</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>74671</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>65247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>74671</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,107 +3355,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3305</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>652</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3295</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3285</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3654</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -3468,74 +3468,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31842</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29189</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31842</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29199</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>89,86%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>98</t>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66569</t>
+          <t>66938</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32494</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>37728</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>32494</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,92 +3698,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5030</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>1905</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>13,95%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1905</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -3811,74 +3811,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30658</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27533</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>31970</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>30658</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>28019</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>31962</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,15%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>86,05%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>96</t>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62061</t>
+          <t>62693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67123</t>
+          <t>67128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -3924,57 +3924,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>32563</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>35161</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>32563</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4097</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1547</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>8784</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,6%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>3296</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7245</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7613</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4097</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1314</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8057</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4159,67 +4159,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>186753</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>182066</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>189303</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,4%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
           <t>183696</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>179747</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>185799</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>179379</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>185781</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>186753</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>182793</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>189536</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>364838</t>
+          <t>364862</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374039</t>
+          <t>373927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>190850</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>186992</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>190850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,107 +4616,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3566</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3440</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4729,74 +4729,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>30680</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>27727</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>27853</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>88,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>89,01%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>98</t>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58698</t>
+          <t>59077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>30918</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>31293</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>30918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4959,72 +4959,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3774</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1149</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3613</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3357</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -5072,74 +5072,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>46703</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>43592</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>49951</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47487</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>47085</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,75%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>46703</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>44009</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>146</t>
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>93254</t>
+          <t>93583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97911</t>
+          <t>97901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47366</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>51100</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47366</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,107 +5302,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1399</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4819</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>1399</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5477</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4277</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1399</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4756</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -5415,74 +5415,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>41401</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>37981</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>41401</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>37323</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>121</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81947</t>
+          <t>82426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>42800</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>43903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>42800</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5758,47 +5758,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>36239</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>27041</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>36239</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>27041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5993,67 +5993,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2062</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4881</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>1762</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>557</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4794</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4830</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5618</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1392</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6101,74 +6101,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>146063</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143244</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>147464</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>160774</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>157742</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>161979</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>157706</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>161982</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>146063</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>142507</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>147469</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>96,21%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>454</t>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302815</t>
+          <t>302713</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309268</t>
+          <t>309269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>148125</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>162536</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>148125</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
